--- a/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,300 +656,312 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E8" s="3">
         <v>14300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6200</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E9" s="3">
         <v>6400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E10" s="3">
         <v>7900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,73 +985,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="E12" s="3">
         <v>5500</v>
       </c>
       <c r="F12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G12" s="3">
         <v>5400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>4700</v>
       </c>
       <c r="H12" s="3">
         <v>4700</v>
       </c>
       <c r="I12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J12" s="3">
         <v>4300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4800</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1119,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1135,8 +1154,8 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1150,15 +1169,15 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1168,8 +1187,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1188,8 +1210,8 @@
       <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
+      <c r="I15" s="3">
+        <v>100</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
@@ -1206,8 +1228,8 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1233,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,138 +1280,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E17" s="3">
         <v>23400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>22000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13800</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7600</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,55 +1442,56 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
@@ -1466,8 +1499,8 @@
       <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>100</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1475,91 +1508,97 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
         <v>0</v>
       </c>
       <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
         <v>-3600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
@@ -1576,113 +1615,119 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>200</v>
       </c>
       <c r="Q22" s="3">
+        <v>200</v>
+      </c>
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>600</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3">
+        <v>-100</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1699,8 +1744,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1735,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1848,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8200</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,55 +2256,58 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
@@ -2246,8 +2315,8 @@
       <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>-100</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2255,73 +2324,79 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8200</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2460,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8200</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,56 +2655,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E41" s="3">
         <v>118200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>133000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>161200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>188400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>193700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>213000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>223100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>224100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>138800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>141300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>149000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>159200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11300</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,20 +2721,23 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E42" s="3">
         <v>29700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19700</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2664,8 +2753,8 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -2700,56 +2789,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15400</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,56 +2857,59 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E44" s="3">
         <v>15900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>13400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>12500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4400</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2830,56 +2925,59 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E45" s="3">
         <v>3100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,56 +2993,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>173800</v>
+      </c>
+      <c r="E46" s="3">
         <v>179800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>181100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>187900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>215600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>223900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>238700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>243000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>252900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>157500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>157200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>163000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>171000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>34400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31500</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3025,22 +3129,25 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E48" s="3">
         <v>9500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10600</v>
-      </c>
-      <c r="G48" s="3">
-        <v>7000</v>
       </c>
       <c r="H48" s="3">
         <v>7000</v>
@@ -3049,32 +3156,32 @@
         <v>7000</v>
       </c>
       <c r="J48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K48" s="3">
         <v>7100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,29 +3197,32 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E49" s="3">
         <v>17700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17200</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,8 +3238,8 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3155,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,8 +3401,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3294,47 +3413,47 @@
         <v>1400</v>
       </c>
       <c r="E52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F52" s="3">
         <v>1300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1200</v>
       </c>
       <c r="K52" s="3">
         <v>1200</v>
       </c>
       <c r="L52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M52" s="3">
         <v>1800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>600</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,56 +3537,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>203000</v>
+      </c>
+      <c r="E54" s="3">
         <v>208500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>210800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>218400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>242600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>249300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>247000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>251200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>260900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>166300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>166500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>171800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>178800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>43400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>39900</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,56 +3659,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3725,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3634,17 +3767,17 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,56 +3793,59 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E59" s="3">
         <v>19700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5600</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,56 +3861,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E60" s="3">
         <v>22300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8500</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,8 +3929,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3805,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>15000</v>
@@ -3829,17 +3971,17 @@
         <v>15000</v>
       </c>
       <c r="O61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="P61" s="3">
         <v>14300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12800</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3855,56 +3997,59 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>16200</v>
+        <v>14900</v>
       </c>
       <c r="E62" s="3">
         <v>16200</v>
       </c>
       <c r="F62" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G62" s="3">
         <v>19100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,56 +4269,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E66" s="3">
         <v>38500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32800</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4377,13 +4544,13 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>71100</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="S70" s="3">
         <v>0</v>
@@ -4400,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,56 +4635,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-170600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-163200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-156100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-146700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-134200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-124400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-118200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-110100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-100600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-97200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-92000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-84600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-78500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-68200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-66500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,56 +4907,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>165500</v>
+      </c>
+      <c r="E76" s="3">
         <v>169900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>174500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>180600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>190600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>196500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>201100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>206800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>214600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>122800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>133300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>139000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-65600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-64000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5043,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8200</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,16 +5212,17 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
@@ -5033,10 +5231,10 @@
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
@@ -5048,40 +5246,43 @@
         <v>300</v>
       </c>
       <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
         <v>500</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,73 +5618,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>200</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-11200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,73 +5714,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,73 +5916,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-100</v>
       </c>
       <c r="L94" s="3">
         <v>-100</v>
       </c>
       <c r="M94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5845,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,50 +6282,53 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-15400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>94500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>137200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -6091,22 +6336,25 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>5000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>17200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6122,8 +6370,8 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -6137,8 +6385,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6170,69 +6418,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>85300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>139500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5700</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
@@ -656,312 +656,325 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6200</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3200</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,76 +999,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E12" s="3">
         <v>5400</v>
-      </c>
-      <c r="E12" s="3">
-        <v>5500</v>
       </c>
       <c r="F12" s="3">
         <v>5500</v>
       </c>
       <c r="G12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H12" s="3">
         <v>5400</v>
-      </c>
-      <c r="H12" s="3">
-        <v>4700</v>
       </c>
       <c r="I12" s="3">
         <v>4700</v>
       </c>
       <c r="J12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4800</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,8 +1139,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1157,8 +1177,8 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1172,15 +1192,15 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1190,8 +1210,11 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1213,8 +1236,8 @@
       <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="J15" s="3">
+        <v>100</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1231,8 +1254,8 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,144 +1307,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E17" s="3">
         <v>24100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>22500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13800</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7600</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,58 +1476,59 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
@@ -1502,8 +1536,8 @@
       <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>100</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1511,97 +1545,103 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1300</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
       <c r="S21" s="3">
         <v>0</v>
       </c>
       <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
         <v>-3600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
@@ -1618,119 +1658,125 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>200</v>
       </c>
       <c r="Q22" s="3">
         <v>200</v>
       </c>
       <c r="R22" s="3">
+        <v>200</v>
+      </c>
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>600</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>-100</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1747,8 +1793,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8200</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,58 +2326,61 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
@@ -2318,8 +2388,8 @@
       <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>-100</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2327,76 +2397,82 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8200</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8200</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,59 +2742,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>104600</v>
+      </c>
+      <c r="E41" s="3">
         <v>121000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>118200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>133000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>161200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>188400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>193700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>213000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>223100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>224100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>138800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>141300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>149000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>159200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11300</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,23 +2811,26 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E42" s="3">
         <v>24600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19700</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2756,8 +2846,8 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2792,59 +2882,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E43" s="3">
         <v>9000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>15400</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,59 +2953,62 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E44" s="3">
         <v>14900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>15900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4400</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2928,59 +3024,62 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E45" s="3">
         <v>4200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,59 +3095,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>161900</v>
+      </c>
+      <c r="E46" s="3">
         <v>173800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>179800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>181100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>187900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>215600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>223900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>238700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>243000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>252900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>157500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>157200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>163000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>171000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>34400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31500</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,8 +3166,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3132,25 +3237,28 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>7000</v>
       </c>
       <c r="I48" s="3">
         <v>7000</v>
@@ -3159,32 +3267,32 @@
         <v>7000</v>
       </c>
       <c r="K48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="L48" s="3">
         <v>7100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7800</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,32 +3308,35 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E49" s="3">
         <v>18200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17200</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3241,8 +3352,8 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,59 +3521,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E52" s="3">
         <v>1400</v>
       </c>
       <c r="F52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G52" s="3">
         <v>1300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1200</v>
       </c>
       <c r="L52" s="3">
         <v>1200</v>
       </c>
       <c r="M52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N52" s="3">
         <v>1800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>600</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,59 +3663,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>189800</v>
+      </c>
+      <c r="E54" s="3">
         <v>203000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>208500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>210800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>218400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>242600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>249300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>247000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>251200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>260900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>166300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>166500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>171800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>178800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>43400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>39900</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,59 +3790,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,8 +3859,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3770,17 +3904,17 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3796,59 +3930,62 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E59" s="3">
         <v>21400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5600</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,59 +4001,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E60" s="3">
         <v>22500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8500</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,8 +4072,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3950,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>15000</v>
@@ -3974,17 +4117,17 @@
         <v>15000</v>
       </c>
       <c r="P61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>14300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12800</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4000,59 +4143,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E62" s="3">
         <v>14900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>16200</v>
       </c>
       <c r="F62" s="3">
         <v>16200</v>
       </c>
       <c r="G62" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H62" s="3">
         <v>19100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,59 +4427,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E66" s="3">
         <v>37500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>38500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>44400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4547,13 +4715,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>71100</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,59 +4809,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-181500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-170600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-163200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-156100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-146700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-134200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-124400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-118200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-110100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-100600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-97200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-92000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-84600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-78500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-68200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-66500</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,59 +5093,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>156900</v>
+      </c>
+      <c r="E76" s="3">
         <v>165500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>169900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>174500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>180600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>190600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>196500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>201100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>206800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>214600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>122800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>126700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>133300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>139000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-65600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-64000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8200</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,19 +5411,20 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
@@ -5234,10 +5433,10 @@
         <v>600</v>
       </c>
       <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
@@ -5249,40 +5448,43 @@
         <v>300</v>
       </c>
       <c r="N83" s="3">
+        <v>300</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
       </c>
       <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>400</v>
-      </c>
-      <c r="S83" s="3">
-        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
         <v>500</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,76 +5835,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>200</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-11200</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,76 +5935,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,76 +6146,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E94" s="3">
         <v>4600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
       </c>
       <c r="N94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,53 +6528,56 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-15400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>94500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>137200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
@@ -6339,22 +6585,25 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>5000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>17200</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6373,8 +6622,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -6388,8 +6637,8 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -6421,72 +6670,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E102" s="3">
         <v>2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-19300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>85300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>139500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5700</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
@@ -656,325 +656,338 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6200</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E9" s="3">
         <v>5000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3200</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E10" s="3">
         <v>5000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E12" s="3">
         <v>5800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5400</v>
-      </c>
-      <c r="F12" s="3">
-        <v>5500</v>
       </c>
       <c r="G12" s="3">
         <v>5500</v>
       </c>
       <c r="H12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I12" s="3">
         <v>5400</v>
-      </c>
-      <c r="I12" s="3">
-        <v>4700</v>
       </c>
       <c r="J12" s="3">
         <v>4700</v>
       </c>
       <c r="K12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L12" s="3">
         <v>4300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4800</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,8 +1159,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1180,8 +1200,8 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1195,15 +1215,15 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,13 +1233,16 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1239,8 +1262,8 @@
       <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>100</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
@@ -1257,8 +1280,8 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E17" s="3">
         <v>22700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13800</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7600</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,61 +1510,62 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
@@ -1539,8 +1573,8 @@
       <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>100</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1548,79 +1582,85 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1300</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
       <c r="T21" s="3">
         <v>0</v>
       </c>
       <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
         <v>-3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1630,21 +1670,21 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
@@ -1661,108 +1701,114 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>200</v>
       </c>
       <c r="R22" s="3">
         <v>200</v>
       </c>
       <c r="S22" s="3">
+        <v>200</v>
+      </c>
+      <c r="T22" s="3">
         <v>500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>600</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1770,16 +1816,16 @@
         <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>-100</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1796,8 +1842,8 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8200</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,61 +2396,64 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
@@ -2391,8 +2461,8 @@
       <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>-100</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2400,79 +2470,85 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8200</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8200</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,62 +2829,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E41" s="3">
         <v>104600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>121000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>118200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>133000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>161200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>188400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>193700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>213000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>223100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>224100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>138800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>141300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>149000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>159200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11300</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,26 +2901,29 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E42" s="3">
         <v>29600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>24600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>29700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19700</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2849,8 +2939,8 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2885,62 +2975,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>15400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,62 +3049,65 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E44" s="3">
         <v>16400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>15900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4400</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,62 +3123,65 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E45" s="3">
         <v>3800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,62 +3197,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E46" s="3">
         <v>161900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>173800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>179800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>181100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>187900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>215600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>223900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>238700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>243000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>252900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>157500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>157200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>163000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>171000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>34400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>31500</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3240,28 +3345,31 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E48" s="3">
         <v>9000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10600</v>
-      </c>
-      <c r="I48" s="3">
-        <v>7000</v>
       </c>
       <c r="J48" s="3">
         <v>7000</v>
@@ -3270,32 +3378,32 @@
         <v>7000</v>
       </c>
       <c r="L48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M48" s="3">
         <v>7100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7800</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,35 +3419,38 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E49" s="3">
         <v>17600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3355,8 +3466,8 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,62 +3641,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1400</v>
       </c>
       <c r="F52" s="3">
         <v>1400</v>
       </c>
       <c r="G52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H52" s="3">
         <v>1300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1200</v>
       </c>
       <c r="M52" s="3">
         <v>1200</v>
       </c>
       <c r="N52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O52" s="3">
         <v>1800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>600</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,62 +3789,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>208800</v>
+      </c>
+      <c r="E54" s="3">
         <v>189800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>203000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>208500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>210800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>218400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>242600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>249300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>247000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>251200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>260900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>166300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>166500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>171800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>178800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>43400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>39900</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,62 +3921,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,8 +3993,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3907,17 +4041,17 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,62 +4067,65 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E59" s="3">
         <v>17900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5600</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,62 +4141,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E60" s="3">
         <v>19300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8500</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,8 +4215,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4096,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>15000</v>
@@ -4120,17 +4263,17 @@
         <v>15000</v>
       </c>
       <c r="Q61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R61" s="3">
         <v>14300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4146,62 +4289,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E62" s="3">
         <v>13600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>16200</v>
       </c>
       <c r="G62" s="3">
         <v>16200</v>
       </c>
       <c r="H62" s="3">
+        <v>16200</v>
+      </c>
+      <c r="I62" s="3">
         <v>19100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,62 +4585,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E66" s="3">
         <v>32900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>38500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>44400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>46300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>43500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4718,13 +4886,13 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>71100</v>
       </c>
       <c r="T70" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,62 +4983,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-194100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-181500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-170600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-163200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-156100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-146700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-134200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-124400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-118200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-110100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-100600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-97200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-92000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-84600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-78500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-68200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-66500</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,62 +5279,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>156400</v>
+      </c>
+      <c r="E76" s="3">
         <v>156900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>165500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>169900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>174500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>180600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>190600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>196500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>201100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>206800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>214600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>122800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>126700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>133300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>139000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-65600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-64000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8200</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,22 +5610,23 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>600</v>
@@ -5436,10 +5635,10 @@
         <v>600</v>
       </c>
       <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
@@ -5451,40 +5650,43 @@
         <v>300</v>
       </c>
       <c r="O83" s="3">
+        <v>300</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
         <v>400</v>
-      </c>
-      <c r="T83" s="3">
-        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
         <v>500</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>200</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-11200</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,79 +6156,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,79 +6376,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-100</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,56 +6774,59 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>94500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>137200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -6588,22 +6834,25 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>5000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>17200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6625,8 +6874,8 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -6640,8 +6889,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6673,75 +6922,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-57800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-19300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>85300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>139500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5700</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>MASS</t>
   </si>
@@ -656,338 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E8" s="3">
         <v>14000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6200</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E9" s="3">
         <v>6600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3200</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E10" s="3">
         <v>7400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3000</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,82 +1027,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E12" s="3">
         <v>6400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>5500</v>
       </c>
       <c r="H12" s="3">
         <v>5500</v>
       </c>
       <c r="I12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J12" s="3">
         <v>5400</v>
-      </c>
-      <c r="J12" s="3">
-        <v>4700</v>
       </c>
       <c r="K12" s="3">
         <v>4700</v>
       </c>
       <c r="L12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M12" s="3">
         <v>4300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4800</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,31 +1179,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+        <v>18400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1203,8 +1223,8 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1218,15 +1238,15 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1236,37 +1256,40 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="L15" s="3">
+        <v>100</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
@@ -1283,8 +1306,8 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,156 +1361,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E17" s="3">
         <v>27600</v>
       </c>
-      <c r="E17" s="3">
-        <v>22700</v>
-      </c>
       <c r="F17" s="3">
-        <v>24100</v>
+        <v>22400</v>
       </c>
       <c r="G17" s="3">
-        <v>23400</v>
+        <v>24400</v>
       </c>
       <c r="H17" s="3">
+        <v>23300</v>
+      </c>
+      <c r="I17" s="3">
         <v>23000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13800</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13600</v>
       </c>
-      <c r="E18" s="3">
-        <v>-12700</v>
-      </c>
       <c r="F18" s="3">
-        <v>-9700</v>
+        <v>-12400</v>
       </c>
       <c r="G18" s="3">
-        <v>-9100</v>
+        <v>-10000</v>
       </c>
       <c r="H18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-10900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7600</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,64 +1544,65 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>1700</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>1500</v>
+        <v>-500</v>
       </c>
       <c r="I20" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
-      </c>
-      <c r="U20" s="3">
-        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
@@ -1576,8 +1610,8 @@
       <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>100</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1585,109 +1619,115 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-12100</v>
+        <v>-10500</v>
       </c>
       <c r="E21" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-9700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="X21" s="3">
         <v>-7000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-11300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-9200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1704,111 +1744,117 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>400</v>
-      </c>
-      <c r="R22" s="3">
-        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
       </c>
       <c r="T22" s="3">
+        <v>200</v>
+      </c>
+      <c r="U22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>600</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8100</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1819,16 +1865,16 @@
         <v>-100</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>-100</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1845,8 +1891,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1881,8 +1927,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8100</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8200</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,64 +2466,67 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-1700</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>-2200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-1900</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-1500</v>
+        <v>500</v>
       </c>
       <c r="I32" s="3">
-        <v>-1000</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-100</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
@@ -2464,8 +2534,8 @@
       <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>-100</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2473,82 +2543,88 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8200</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8200</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,65 +2916,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E41" s="3">
         <v>46800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>104600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>121000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>118200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>133000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>161200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>188400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>193700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>213000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>223100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>224100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>138800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>141300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>149000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>159200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11300</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,31 +2991,34 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E42" s="3">
         <v>30600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>24600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>29700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>19700</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2942,8 +3032,8 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2978,65 +3068,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E43" s="3">
         <v>11000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>15400</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,65 +3145,68 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E44" s="3">
         <v>18600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4400</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3126,65 +3222,68 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N45" s="3">
         <v>3900</v>
       </c>
-      <c r="I45" s="3">
-        <v>5200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3400</v>
-      </c>
-      <c r="M45" s="3">
-        <v>3900</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,65 +3299,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E46" s="3">
         <v>110400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>161900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>173800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>179800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>181100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>187900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>215600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>223900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>238700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>243000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>252900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>157500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>157200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>163000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>171000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>34400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>31500</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,31 +3376,34 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3348,31 +3453,34 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E48" s="3">
         <v>9500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>7000</v>
       </c>
       <c r="K48" s="3">
         <v>7000</v>
@@ -3381,32 +3489,32 @@
         <v>7000</v>
       </c>
       <c r="M48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N48" s="3">
         <v>7100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3422,38 +3530,41 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E49" s="3">
         <v>87500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3580,8 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,8 +3761,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3653,56 +3773,56 @@
         <v>1400</v>
       </c>
       <c r="E52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F52" s="3">
         <v>1300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1400</v>
       </c>
       <c r="G52" s="3">
         <v>1400</v>
       </c>
       <c r="H52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I52" s="3">
         <v>1300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1200</v>
       </c>
       <c r="N52" s="3">
         <v>1200</v>
       </c>
       <c r="O52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P52" s="3">
         <v>1800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,65 +3915,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>178300</v>
+      </c>
+      <c r="E54" s="3">
         <v>208800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>189800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>203000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>208500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>210800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>218400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>242600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>249300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>247000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>251200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>260900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>166300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>166500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>171800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>178800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>43400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>39900</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,65 +4052,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,31 +4127,34 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4044,17 +4178,17 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,65 +4204,68 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>19700</v>
+        <v>14800</v>
       </c>
       <c r="E59" s="3">
-        <v>17900</v>
+        <v>12800</v>
       </c>
       <c r="F59" s="3">
-        <v>21400</v>
+        <v>11300</v>
       </c>
       <c r="G59" s="3">
-        <v>19700</v>
+        <v>12100</v>
       </c>
       <c r="H59" s="3">
-        <v>18700</v>
+        <v>12300</v>
       </c>
       <c r="I59" s="3">
-        <v>16900</v>
+        <v>12600</v>
       </c>
       <c r="J59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K59" s="3">
         <v>17800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5600</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,65 +4281,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E60" s="3">
         <v>21700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8500</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,31 +4358,34 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J61" s="3">
-        <v>15000</v>
+        <v>5500</v>
       </c>
       <c r="K61" s="3">
         <v>15000</v>
@@ -4266,17 +4409,17 @@
         <v>15000</v>
       </c>
       <c r="R61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S61" s="3">
         <v>14300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12800</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4292,65 +4435,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>30700</v>
+        <v>3400</v>
       </c>
       <c r="E62" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
+        <v>200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3">
+        <v>17800</v>
+      </c>
+      <c r="L62" s="3">
+        <v>18700</v>
+      </c>
+      <c r="M62" s="3">
+        <v>15400</v>
+      </c>
+      <c r="N62" s="3">
+        <v>15800</v>
+      </c>
+      <c r="O62" s="3">
+        <v>16500</v>
+      </c>
+      <c r="P62" s="3">
+        <v>15500</v>
+      </c>
+      <c r="Q62" s="3">
         <v>13600</v>
       </c>
-      <c r="F62" s="3">
-        <v>14900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>16200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>16200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>19100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>17800</v>
-      </c>
-      <c r="K62" s="3">
-        <v>18700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>15400</v>
-      </c>
-      <c r="M62" s="3">
-        <v>15800</v>
-      </c>
-      <c r="N62" s="3">
-        <v>16500</v>
-      </c>
-      <c r="O62" s="3">
-        <v>15500</v>
-      </c>
-      <c r="P62" s="3">
-        <v>13600</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,65 +4743,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E66" s="3">
         <v>52400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>44400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>46300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32800</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4889,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>71100</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,65 +5157,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-223400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-194100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-181500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-170600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-163200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-156100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-146700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-134200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-124400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-118200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-110100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-100600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-97200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-84600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-78500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-68200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-66500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,65 +5465,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E76" s="3">
         <v>156400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>156900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>165500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>169900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>174500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>180600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>190600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>196500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>201100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>206800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>214600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>122800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>126700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>133300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>139000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-65600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-64000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8200</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,8 +5809,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5620,28 +5819,28 @@
         <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
       </c>
       <c r="G83" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="I83" s="3">
-        <v>600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>600</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
@@ -5653,40 +5852,43 @@
         <v>300</v>
       </c>
       <c r="P83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
         <v>400</v>
-      </c>
-      <c r="U83" s="3">
-        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
         <v>500</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>200</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-11200</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,82 +6377,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>600</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,82 +6606,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-45100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-100</v>
       </c>
       <c r="O94" s="3">
         <v>-100</v>
       </c>
       <c r="P94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,31 +6714,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,59 +7020,62 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>94500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>137200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -6837,22 +7083,25 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>5000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>17200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6871,14 +7120,14 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -6892,8 +7141,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6925,78 +7174,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-57800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-28200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-19300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>85300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>139500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5700</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>MASS</t>
   </si>
@@ -656,351 +656,363 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E8" s="3">
         <v>16800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6200</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E9" s="3">
         <v>8400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3200</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E10" s="3">
         <v>8300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1040,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E12" s="3">
         <v>6800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5400</v>
-      </c>
-      <c r="H12" s="3">
-        <v>5500</v>
       </c>
       <c r="I12" s="3">
         <v>5500</v>
       </c>
       <c r="J12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K12" s="3">
         <v>5400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>4700</v>
       </c>
       <c r="L12" s="3">
         <v>4700</v>
       </c>
       <c r="M12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N12" s="3">
         <v>4300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4800</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,74 +1198,77 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E14" s="3">
         <v>18400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-300</v>
       </c>
-      <c r="H14" s="3">
-        <v>100</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,8 +1278,11 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1268,31 +1290,31 @@
         <v>1400</v>
       </c>
       <c r="E15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F15" s="3">
         <v>500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>600</v>
       </c>
       <c r="J15" s="3">
         <v>600</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>100</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1309,8 +1331,8 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1336,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1387,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E17" s="3">
         <v>28600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22400</v>
       </c>
-      <c r="G17" s="3">
-        <v>24400</v>
-      </c>
       <c r="H17" s="3">
+        <v>24300</v>
+      </c>
+      <c r="I17" s="3">
         <v>23300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13800</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-10000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-9000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,8 +1577,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1554,58 +1587,58 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
-      </c>
-      <c r="V20" s="3">
-        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
@@ -1613,8 +1646,8 @@
       <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>100</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1622,85 +1655,91 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-9700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-7800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-9100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1300</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
         <v>0</v>
       </c>
       <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>-3600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1713,24 +1752,24 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1747,114 +1786,120 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
-      </c>
-      <c r="S22" s="3">
-        <v>200</v>
       </c>
       <c r="T22" s="3">
         <v>200</v>
       </c>
       <c r="U22" s="3">
+        <v>200</v>
+      </c>
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>600</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-29400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1868,16 +1913,16 @@
         <v>-100</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>-100</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1894,8 +1939,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1930,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2055,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-29300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-29300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,8 +2535,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2478,58 +2547,58 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
@@ -2537,8 +2606,8 @@
       <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>-100</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2546,85 +2615,91 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-29300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2775,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-29300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,68 +3002,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E41" s="3">
         <v>45000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>46800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>104600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>121000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>118200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>133000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>161200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>188400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>193700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>213000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>223100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>224100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>138800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>141300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>149000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>159200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11300</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,34 +3080,37 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E42" s="3">
         <v>26700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>30600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>29600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>24600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19700</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -3035,8 +3124,8 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -3071,68 +3160,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E43" s="3">
         <v>16700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>15400</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,68 +3240,71 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E44" s="3">
         <v>17800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>18600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>15900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4400</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,8 +3320,11 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3251,42 +3349,42 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>4700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,68 +3400,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>103100</v>
+      </c>
+      <c r="E46" s="3">
         <v>108900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>110400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>161900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>173800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>179800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>181100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>187900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>215600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>223900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>238700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>243000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>252900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>157500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>157200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>163000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>171000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>34400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>31500</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3405,8 +3509,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3456,34 +3560,37 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E48" s="3">
         <v>11200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>7000</v>
       </c>
       <c r="L48" s="3">
         <v>7000</v>
@@ -3492,32 +3599,32 @@
         <v>7000</v>
       </c>
       <c r="N48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="O48" s="3">
         <v>7100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,41 +3640,44 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E49" s="3">
         <v>56800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>87500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,8 +3693,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3610,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,68 +3880,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1400</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
         <v>1400</v>
       </c>
       <c r="F52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G52" s="3">
         <v>1300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1400</v>
       </c>
       <c r="H52" s="3">
         <v>1400</v>
       </c>
       <c r="I52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1300</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1200</v>
       </c>
       <c r="O52" s="3">
         <v>1200</v>
       </c>
       <c r="P52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>600</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,68 +4040,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>159500</v>
+      </c>
+      <c r="E54" s="3">
         <v>178300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>208800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>189800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>203000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>208500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>210800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>218400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>242600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>249300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>247000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>251200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>260900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>166300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>166500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>171800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>178800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>39900</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,68 +4182,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,35 +4260,38 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
         <v>2300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2000</v>
       </c>
       <c r="H58" s="3">
         <v>2000</v>
       </c>
       <c r="I58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J58" s="3">
         <v>1900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4181,17 +4314,17 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,68 +4340,71 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E59" s="3">
         <v>14800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5600</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,68 +4420,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E60" s="3">
         <v>25700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8500</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,34 +4500,37 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E61" s="3">
         <v>4900</v>
-      </c>
-      <c r="E61" s="3">
-        <v>3400</v>
       </c>
       <c r="F61" s="3">
         <v>3400</v>
       </c>
       <c r="G61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H61" s="3">
         <v>3900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>15000</v>
       </c>
       <c r="L61" s="3">
         <v>15000</v>
@@ -4412,17 +4554,17 @@
         <v>15000</v>
       </c>
       <c r="S61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="T61" s="3">
         <v>14300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12800</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4438,68 +4580,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E62" s="3">
         <v>3400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15500</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,68 +4900,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E66" s="3">
         <v>47200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>52400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>38500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>44400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>46300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>39800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32800</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5060,13 +5227,13 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>71100</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5083,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,68 +5330,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-242800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-223400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-194100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-181500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-170600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-163200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-156100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-146700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-134200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-124400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-118200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-110100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-100600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-97200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-92000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-84600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-78500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-68200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-66500</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,68 +5650,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>114600</v>
+      </c>
+      <c r="E76" s="3">
         <v>131000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>156400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>156900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>165500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>169900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>174500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>180600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>190600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>196500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>201100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>206800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>214600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>122800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>126700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>133300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>139000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-65600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-64000</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5810,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-29300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,16 +6007,17 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
@@ -5828,7 +6026,7 @@
         <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
         <v>300</v>
@@ -5837,13 +6035,13 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
+        <v>300</v>
+      </c>
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
@@ -5855,40 +6053,43 @@
         <v>300</v>
       </c>
       <c r="Q83" s="3">
+        <v>300</v>
+      </c>
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
         <v>400</v>
-      </c>
-      <c r="V83" s="3">
-        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
       </c>
       <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>500</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6485,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,8 +6597,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6387,76 +6607,79 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,85 +6835,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>800</v>
+      </c>
+      <c r="E94" s="3">
         <v>3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-45100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
       </c>
       <c r="Q94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6741,8 +6974,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6792,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,62 +7265,65 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-15400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>94500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>137200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -7086,22 +7331,25 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>5000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>17200</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7120,17 +7368,17 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
@@ -7144,8 +7392,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7177,81 +7425,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-57800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>85300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>139500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5700</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>MASS</t>
   </si>
@@ -656,363 +656,376 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E8" s="3">
         <v>18800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14000</v>
       </c>
-      <c r="G8" s="3">
-        <v>10000</v>
-      </c>
       <c r="H8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I8" s="3">
         <v>14400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>15100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6200</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E9" s="3">
         <v>9600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6600</v>
       </c>
-      <c r="G9" s="3">
-        <v>5000</v>
-      </c>
       <c r="H9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I9" s="3">
         <v>7100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3200</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E10" s="3">
         <v>9200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7400</v>
       </c>
-      <c r="G10" s="3">
-        <v>5000</v>
-      </c>
       <c r="H10" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I10" s="3">
         <v>7300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3000</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,88 +1054,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E12" s="3">
         <v>6400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6400</v>
       </c>
-      <c r="G12" s="3">
-        <v>5800</v>
-      </c>
       <c r="H12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I12" s="3">
         <v>5400</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5500</v>
       </c>
       <c r="J12" s="3">
         <v>5500</v>
       </c>
       <c r="K12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L12" s="3">
         <v>5400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>4700</v>
       </c>
       <c r="M12" s="3">
         <v>4700</v>
       </c>
       <c r="N12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="O12" s="3">
         <v>4300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4800</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,37 +1218,40 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E14" s="3">
         <v>9800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>300</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1248,8 +1268,8 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1263,15 +1283,15 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-300</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1281,43 +1301,46 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
         <v>1400</v>
       </c>
       <c r="F15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G15" s="3">
         <v>500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
       </c>
       <c r="L15" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>100</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
@@ -1334,8 +1357,8 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,168 +1414,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E17" s="3">
         <v>29300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27600</v>
       </c>
-      <c r="G17" s="3">
-        <v>22400</v>
-      </c>
       <c r="H17" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I17" s="3">
         <v>24300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13800</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-12400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-9900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,70 +1611,71 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
-      </c>
-      <c r="W20" s="3">
-        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
@@ -1649,8 +1683,8 @@
       <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>100</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
@@ -1658,88 +1692,94 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-11100</v>
-      </c>
       <c r="H21" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-9600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1300</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
         <v>0</v>
       </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1755,24 +1795,24 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1789,122 +1829,128 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
-      </c>
-      <c r="T22" s="3">
-        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
       </c>
       <c r="V22" s="3">
+        <v>200</v>
+      </c>
+      <c r="W22" s="3">
         <v>500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>600</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-29400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-11000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-7400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>-100</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
         <v>-100</v>
@@ -1915,17 +1961,17 @@
       <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="K24" s="3">
+        <v>-100</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
@@ -1942,8 +1988,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,168 +2107,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-10900</v>
-      </c>
       <c r="H26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8100</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,13 +2356,16 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>53400</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2316,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2378,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,70 +2605,73 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
@@ -2609,8 +2679,8 @@
       <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>-100</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
@@ -2618,88 +2688,94 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,173 +2854,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,71 +3089,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E41" s="3">
         <v>44000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>46800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>104600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>121000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>118200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>133000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>161200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>188400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>193700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>213000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>223100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>224100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>138800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>141300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>149000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>159200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,37 +3170,40 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E42" s="3">
         <v>25600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>30600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>29600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>24600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>29700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>19700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -3127,8 +3217,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3163,71 +3253,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E43" s="3">
         <v>12600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>15400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,71 +3336,74 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E44" s="3">
         <v>16200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>15900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4400</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3323,8 +3419,11 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3352,42 +3451,42 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>4700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,71 +3502,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E46" s="3">
         <v>103100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>108900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>110400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>161900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>173800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>179800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>181100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>187900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>215600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>223900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>238700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>243000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>252900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>157500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>157200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>163000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>171000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>34400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>31500</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,8 +3585,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3512,8 +3617,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3563,37 +3668,40 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E48" s="3">
         <v>10300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10600</v>
-      </c>
-      <c r="L48" s="3">
-        <v>7000</v>
       </c>
       <c r="M48" s="3">
         <v>7000</v>
@@ -3602,32 +3710,32 @@
         <v>7000</v>
       </c>
       <c r="O48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P48" s="3">
         <v>7100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,44 +3751,47 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E49" s="3">
         <v>45300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>56800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>87500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3696,8 +3807,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,71 +4000,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1400</v>
       </c>
       <c r="F52" s="3">
         <v>1400</v>
       </c>
       <c r="G52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H52" s="3">
         <v>1300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1400</v>
       </c>
       <c r="I52" s="3">
         <v>1400</v>
       </c>
       <c r="J52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K52" s="3">
         <v>1300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1300</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1200</v>
       </c>
       <c r="P52" s="3">
         <v>1200</v>
       </c>
       <c r="Q52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R52" s="3">
         <v>1800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,71 +4166,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E54" s="3">
         <v>159500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>178300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>208800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>189800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>203000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>208500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>210800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>218400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>242600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>249300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>247000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>251200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>260900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>166300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>166500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>171800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>178800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>43400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>39900</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,71 +4313,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,38 +4394,41 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2000</v>
       </c>
       <c r="I58" s="3">
         <v>2000</v>
       </c>
       <c r="J58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K58" s="3">
         <v>1900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4317,17 +4451,17 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4343,71 +4477,74 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E59" s="3">
         <v>13100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5600</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,71 +4560,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E60" s="3">
         <v>25100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8500</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,37 +4643,40 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E61" s="3">
         <v>4700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>3400</v>
       </c>
       <c r="G61" s="3">
         <v>3400</v>
       </c>
       <c r="H61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I61" s="3">
         <v>3900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5500</v>
-      </c>
-      <c r="L61" s="3">
-        <v>15000</v>
       </c>
       <c r="M61" s="3">
         <v>15000</v>
@@ -4557,17 +4700,17 @@
         <v>15000</v>
       </c>
       <c r="T61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="U61" s="3">
         <v>14300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12800</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4583,71 +4726,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15500</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>14300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,71 +5058,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E66" s="3">
         <v>44900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>52400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>38500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>44400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>46300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>43500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>39800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>37900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32800</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5230,13 +5398,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>71100</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,71 +5504,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-199200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-242800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-223400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-194100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-181500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-170600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-163200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-156100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-146700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-134200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-124400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-118200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-110100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-100600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-97200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-92000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-84600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-78500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-68200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-66500</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,71 +5836,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>159400</v>
+      </c>
+      <c r="E76" s="3">
         <v>114600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>131000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>156400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>156900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>165500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>169900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>174500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>180600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>190600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>196500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>201100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>206800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>214600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>122800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>126700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>133300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>139000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-65600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-64000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,173 +6002,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,19 +6206,20 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>400</v>
       </c>
       <c r="G83" s="3">
         <v>400</v>
@@ -6029,7 +6228,7 @@
         <v>400</v>
       </c>
       <c r="I83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
@@ -6038,13 +6237,13 @@
         <v>300</v>
       </c>
       <c r="L83" s="3">
+        <v>300</v>
+      </c>
+      <c r="M83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
@@ -6056,40 +6255,43 @@
         <v>300</v>
       </c>
       <c r="R83" s="3">
+        <v>300</v>
+      </c>
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100</v>
-      </c>
-      <c r="T83" s="3">
-        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
         <v>400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
       </c>
       <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>500</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,88 +6702,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>200</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,8 +6818,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6610,76 +6831,79 @@
         <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
       </c>
       <c r="R91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,88 +7065,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E94" s="3">
         <v>800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-45100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-100</v>
       </c>
       <c r="Q94" s="3">
         <v>-100</v>
       </c>
       <c r="R94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6977,8 +7211,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,65 +7511,68 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-15400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>94500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>137200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -7334,22 +7580,25 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>5000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>17200</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7371,17 +7620,17 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -7395,8 +7644,8 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -7428,84 +7677,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-57800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>85300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>139500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5700</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>MASS</t>
   </si>
@@ -656,376 +656,389 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E8" s="3">
         <v>11800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16800</v>
       </c>
-      <c r="G8" s="3">
-        <v>14000</v>
-      </c>
       <c r="H8" s="3">
+        <v>11500</v>
+      </c>
+      <c r="I8" s="3">
         <v>7400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6200</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E9" s="3">
         <v>6200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>5300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>7100</v>
+      </c>
+      <c r="K9" s="3">
+        <v>6400</v>
+      </c>
+      <c r="L9" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M9" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="O9" s="3">
+        <v>6500</v>
+      </c>
+      <c r="P9" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>4200</v>
+      </c>
+      <c r="R9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="S9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="T9" s="3">
+        <v>3900</v>
+      </c>
+      <c r="U9" s="3">
+        <v>2600</v>
+      </c>
+      <c r="V9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="W9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X9" s="3">
         <v>6600</v>
       </c>
-      <c r="H9" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J9" s="3">
-        <v>6400</v>
-      </c>
-      <c r="K9" s="3">
-        <v>6300</v>
-      </c>
-      <c r="L9" s="3">
-        <v>5100</v>
-      </c>
-      <c r="M9" s="3">
-        <v>5700</v>
-      </c>
-      <c r="N9" s="3">
-        <v>6500</v>
-      </c>
-      <c r="O9" s="3">
-        <v>4500</v>
-      </c>
-      <c r="P9" s="3">
-        <v>4200</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>6700</v>
-      </c>
-      <c r="R9" s="3">
-        <v>5700</v>
-      </c>
-      <c r="S9" s="3">
-        <v>3900</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="Y9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z9" s="3">
         <v>2600</v>
       </c>
-      <c r="U9" s="3">
-        <v>3100</v>
-      </c>
-      <c r="V9" s="3">
-        <v>2200</v>
-      </c>
-      <c r="W9" s="3">
-        <v>6600</v>
-      </c>
-      <c r="X9" s="3">
-        <v>4000</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>2600</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3200</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E10" s="3">
         <v>5500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8300</v>
       </c>
-      <c r="G10" s="3">
-        <v>7400</v>
-      </c>
       <c r="H10" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I10" s="3">
         <v>3900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3000</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,91 +1068,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E12" s="3">
         <v>3800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6800</v>
       </c>
-      <c r="G12" s="3">
-        <v>6400</v>
-      </c>
       <c r="H12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I12" s="3">
         <v>3300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5400</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5500</v>
       </c>
       <c r="K12" s="3">
         <v>5500</v>
       </c>
       <c r="L12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="M12" s="3">
         <v>5400</v>
-      </c>
-      <c r="M12" s="3">
-        <v>4700</v>
       </c>
       <c r="N12" s="3">
         <v>4700</v>
       </c>
       <c r="O12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P12" s="3">
         <v>4300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4800</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,40 +1238,43 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E14" s="3">
         <v>2500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>9800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>18400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1271,8 +1291,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1286,15 +1306,15 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1304,46 +1324,49 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1400</v>
       </c>
       <c r="F15" s="3">
         <v>1400</v>
       </c>
       <c r="G15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>600</v>
       </c>
       <c r="M15" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="N15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>100</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1360,8 +1383,8 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1387,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,174 +1441,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E17" s="3">
         <v>20300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28600</v>
       </c>
-      <c r="G17" s="3">
-        <v>27600</v>
-      </c>
       <c r="H17" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I17" s="3">
         <v>15000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13800</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-13600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-7600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,73 +1645,74 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
-      </c>
-      <c r="X20" s="3">
-        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>100</v>
@@ -1686,8 +1720,8 @@
       <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
+      <c r="AA20" s="3">
+        <v>100</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
@@ -1695,91 +1729,97 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-13200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-6300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1300</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
       <c r="X21" s="3">
         <v>0</v>
       </c>
       <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1798,24 +1838,24 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1832,128 +1872,134 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
-      </c>
-      <c r="U22" s="3">
-        <v>200</v>
       </c>
       <c r="V22" s="3">
         <v>200</v>
       </c>
       <c r="W22" s="3">
+        <v>200</v>
+      </c>
+      <c r="X22" s="3">
         <v>500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>600</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-29400</v>
       </c>
-      <c r="G23" s="3">
-        <v>-12600</v>
-      </c>
       <c r="H23" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-5900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8100</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-100</v>
+      <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>-100</v>
@@ -1964,17 +2010,17 @@
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>-100</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1991,8 +2037,8 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -2027,8 +2073,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,174 +2159,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-29300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="M26" s="3">
         <v>-12500</v>
       </c>
-      <c r="H26" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="N26" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="T26" s="3">
         <v>-7400</v>
       </c>
-      <c r="J26" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-12500</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="U26" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="W26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-8100</v>
       </c>
-      <c r="P26" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E27" s="3">
         <v>43600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-29300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,16 +2417,19 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E29" s="3">
         <v>53400</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2380,7 +2441,7 @@
         <v>-5000</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2442,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,73 +2675,76 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-100</v>
       </c>
       <c r="Y32" s="3">
         <v>-100</v>
@@ -2682,8 +2752,8 @@
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
+      <c r="AA32" s="3">
+        <v>-100</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
@@ -2691,91 +2761,97 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E33" s="3">
         <v>43600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-29300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,179 +2933,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E35" s="3">
         <v>43600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-29300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,74 +3176,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E41" s="3">
         <v>79200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>44000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>45000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>46800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>104600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>121000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>118200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>161200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>188400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>193700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>213000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>223100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>224100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>138800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>141300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>149000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>159200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11300</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,40 +3260,43 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E42" s="3">
         <v>45200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>30600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>24600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>29700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>19700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -3220,8 +3310,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3256,74 +3346,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E43" s="3">
         <v>6900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>15400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3339,74 +3432,77 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E44" s="3">
         <v>12700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>15900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4400</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3422,13 +3518,16 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>500</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -3454,42 +3553,42 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>4700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,74 +3604,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>147900</v>
+      </c>
+      <c r="E46" s="3">
         <v>149000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>103100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>108900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>110400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>161900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>173800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>179800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>181100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>187900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>215600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>223900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>238700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>243000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>252900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>157500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>157200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>163000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>171000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>34400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>31500</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,8 +3690,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3620,8 +3725,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3671,40 +3776,43 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10600</v>
-      </c>
-      <c r="M48" s="3">
-        <v>7000</v>
       </c>
       <c r="N48" s="3">
         <v>7000</v>
@@ -3713,32 +3821,32 @@
         <v>7000</v>
       </c>
       <c r="P48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>7100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3754,47 +3862,50 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E49" s="3">
         <v>38000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>45300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>56800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>87500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3810,8 +3921,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3837,8 +3948,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,74 +4120,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>600</v>
+      </c>
+      <c r="E52" s="3">
         <v>4000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>800</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1400</v>
       </c>
       <c r="G52" s="3">
         <v>1400</v>
       </c>
       <c r="H52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I52" s="3">
         <v>1300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1400</v>
       </c>
       <c r="J52" s="3">
         <v>1400</v>
       </c>
       <c r="K52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L52" s="3">
         <v>1300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1300</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1200</v>
       </c>
       <c r="Q52" s="3">
         <v>1200</v>
       </c>
       <c r="R52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S52" s="3">
         <v>1800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>600</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,8 +4206,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,74 +4292,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>191700</v>
+      </c>
+      <c r="E54" s="3">
         <v>196000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>159500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>178300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>208800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>189800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>203000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>208500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>210800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>218400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>242600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>249300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>247000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>251200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>260900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>166300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>166500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>171800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>178800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>43400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>39900</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4378,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,74 +4444,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>900</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,41 +4528,44 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2000</v>
       </c>
       <c r="J58" s="3">
         <v>2000</v>
       </c>
       <c r="K58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L58" s="3">
         <v>1900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1700</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4454,17 +4588,17 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4480,74 +4614,77 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E59" s="3">
         <v>10500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5600</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,74 +4700,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E60" s="3">
         <v>19600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8500</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4646,40 +4786,43 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4900</v>
-      </c>
-      <c r="G61" s="3">
-        <v>3400</v>
       </c>
       <c r="H61" s="3">
         <v>3400</v>
       </c>
       <c r="I61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J61" s="3">
         <v>3900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>15000</v>
       </c>
       <c r="N61" s="3">
         <v>15000</v>
@@ -4703,17 +4846,17 @@
         <v>15000</v>
       </c>
       <c r="U61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="V61" s="3">
         <v>14300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12800</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4729,74 +4872,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>4800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15500</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>14600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>14300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11500</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,8 +4958,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,74 +5216,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E66" s="3">
         <v>36600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>44900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>38500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>44400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>46300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>43500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>39800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>38400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>39800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>37900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>32800</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5302,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5401,13 +5569,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>71100</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5424,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,74 +5678,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-212500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-199200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-242800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-223400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-194100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-181500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-170600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-163200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-156100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-146700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-134200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-124400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-118200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-110100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-100600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-97200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-92000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-84600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-78500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-68200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-66500</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5590,8 +5764,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,74 +6022,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>148800</v>
+      </c>
+      <c r="E76" s="3">
         <v>159400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>114600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>131000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>156400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>156900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>165500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>169900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>174500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>180600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>190600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>196500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>201100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>206800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>214600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>122800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>126700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>133300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>139000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-65600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-64000</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5922,8 +6108,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,179 +6194,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E81" s="3">
         <v>43600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-29300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,22 +6405,23 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>400</v>
       </c>
       <c r="H83" s="3">
         <v>400</v>
@@ -6231,7 +6430,7 @@
         <v>400</v>
       </c>
       <c r="J83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
@@ -6240,13 +6439,13 @@
         <v>300</v>
       </c>
       <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
@@ -6258,40 +6457,43 @@
         <v>300</v>
       </c>
       <c r="S83" s="3">
+        <v>300</v>
+      </c>
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
         <v>400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
       </c>
       <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>500</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,91 +6919,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>200</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,13 +7039,14 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
@@ -6834,76 +7055,79 @@
         <v>-200</v>
       </c>
       <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
         <v>600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,91 +7295,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E94" s="3">
         <v>50300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-45100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7214,8 +7448,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7265,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,68 +7757,71 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>94500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>137200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -7583,22 +7829,25 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>5000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>17200</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7623,17 +7872,17 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
@@ -7647,8 +7896,8 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -7680,87 +7929,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E102" s="3">
         <v>35100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-57800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-27200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>85300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>139500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5700</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>MASS</t>
   </si>
@@ -656,402 +656,414 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E8" s="3">
         <v>14000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11800</v>
       </c>
-      <c r="G8" s="3">
-        <v>18800</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>14500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>15100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6200</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>6700</v>
+        <v>8200</v>
       </c>
       <c r="E9" s="3">
         <v>6700</v>
       </c>
       <c r="F9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G9" s="3">
         <v>6200</v>
       </c>
-      <c r="G9" s="3">
-        <v>9600</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
         <v>6700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3200</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E10" s="3">
         <v>7400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5500</v>
       </c>
-      <c r="G10" s="3">
-        <v>9200</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
         <v>7800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3000</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,97 +1095,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E12" s="3">
         <v>3800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3800</v>
       </c>
-      <c r="G12" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
         <v>4200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>5500</v>
       </c>
       <c r="M12" s="3">
         <v>5500</v>
       </c>
       <c r="N12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="O12" s="3">
         <v>5400</v>
-      </c>
-      <c r="O12" s="3">
-        <v>4700</v>
       </c>
       <c r="P12" s="3">
         <v>4700</v>
       </c>
       <c r="Q12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="R12" s="3">
         <v>4300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4800</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,46 +1277,49 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E14" s="3">
         <v>10700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2500</v>
       </c>
-      <c r="G14" s="3">
-        <v>9800</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>18400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1317,8 +1336,8 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
@@ -1332,15 +1351,15 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-300</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1369,11 @@
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1359,43 +1381,43 @@
         <v>1100</v>
       </c>
       <c r="E15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1400</v>
       </c>
       <c r="H15" s="3">
         <v>1400</v>
       </c>
       <c r="I15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>700</v>
-      </c>
-      <c r="M15" s="3">
-        <v>600</v>
       </c>
       <c r="N15" s="3">
         <v>600</v>
       </c>
       <c r="O15" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="P15" s="3">
         <v>100</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>100</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
@@ -1412,8 +1434,8 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1439,8 +1461,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1469,186 +1494,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E17" s="3">
         <v>19600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20300</v>
       </c>
-      <c r="G17" s="3">
-        <v>29300</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
         <v>20600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>19400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13800</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
         <v>-6100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1680,79 +1712,80 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>100</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
@@ -1760,8 +1793,8 @@
       <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
+      <c r="AC20" s="3">
+        <v>100</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
@@ -1769,97 +1802,103 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="S21" s="3">
         <v>-9100</v>
       </c>
-      <c r="H21" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-9200</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
       <c r="Z21" s="3">
         <v>0</v>
       </c>
       <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1884,24 +1923,24 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1918,140 +1957,146 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>400</v>
-      </c>
-      <c r="W22" s="3">
-        <v>200</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
       </c>
       <c r="Y22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z22" s="3">
         <v>500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>600</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-19500</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3">
         <v>-23600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8100</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-100</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -2062,17 +2107,17 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>-100</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -2089,8 +2134,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2125,8 +2170,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2214,186 +2262,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9800</v>
       </c>
-      <c r="G26" s="3">
-        <v>-19400</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3">
         <v>-23600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-8100</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>43600</v>
       </c>
-      <c r="G27" s="3">
-        <v>-19400</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
         <v>-29300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2481,34 +2538,37 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E29" s="3">
         <v>-100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>53400</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-5600</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-5000</v>
       </c>
       <c r="J29" s="3">
         <v>-5000</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2570,8 +2630,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2659,8 +2722,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2748,79 +2814,82 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-100</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
@@ -2828,8 +2897,8 @@
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
+      <c r="AC32" s="3">
+        <v>-100</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
@@ -2837,97 +2906,103 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>43600</v>
       </c>
-      <c r="G33" s="3">
-        <v>-19400</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3">
         <v>-29300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3015,191 +3090,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>43600</v>
       </c>
-      <c r="G35" s="3">
-        <v>-19400</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3">
         <v>-29300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3231,8 +3315,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3264,80 +3349,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E41" s="3">
         <v>62800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>61800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>79200</v>
       </c>
-      <c r="G41" s="3">
-        <v>44000</v>
-      </c>
       <c r="H41" s="3">
+        <v>43400</v>
+      </c>
+      <c r="I41" s="3">
         <v>45000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>104600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>121000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>118200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>133000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>161200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>188400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>193700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>213000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>223100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>224100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>138800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>141300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>149000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>159200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11300</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,46 +3439,49 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E42" s="3">
         <v>49300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>56800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>45200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>29600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>24600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>29700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>19700</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
@@ -3406,8 +3495,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3442,80 +3531,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E43" s="3">
         <v>11000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6900</v>
       </c>
-      <c r="G43" s="3">
-        <v>12600</v>
-      </c>
       <c r="H43" s="3">
+        <v>8900</v>
+      </c>
+      <c r="I43" s="3">
         <v>16700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>15400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3531,80 +3623,83 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E44" s="3">
         <v>15300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>15500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>12700</v>
       </c>
-      <c r="G44" s="3">
-        <v>16200</v>
-      </c>
       <c r="H44" s="3">
+        <v>10900</v>
+      </c>
+      <c r="I44" s="3">
         <v>17800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>15900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>11700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>11200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4400</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3620,25 +3715,28 @@
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>10200</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -3658,42 +3756,42 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>4700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,80 +3807,83 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>144600</v>
+      </c>
+      <c r="E46" s="3">
         <v>144900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>147900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>149000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>103100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>108900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>110400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>161900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>173800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>179800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>181100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>187900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>215600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>223900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>238700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>243000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>252900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>157500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>157200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>163000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>171000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>34400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>31500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,8 +3899,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3836,8 +3940,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3887,46 +3991,49 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E48" s="3">
         <v>8300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5100</v>
       </c>
-      <c r="G48" s="3">
-        <v>10300</v>
-      </c>
       <c r="H48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I48" s="3">
         <v>11200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10600</v>
-      </c>
-      <c r="O48" s="3">
-        <v>7000</v>
       </c>
       <c r="P48" s="3">
         <v>7000</v>
@@ -3935,32 +4042,32 @@
         <v>7000</v>
       </c>
       <c r="R48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="S48" s="3">
         <v>7100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7800</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3976,53 +4083,56 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E49" s="3">
         <v>37100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>37300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>38000</v>
       </c>
-      <c r="G49" s="3">
-        <v>45300</v>
-      </c>
       <c r="H49" s="3">
+        <v>38700</v>
+      </c>
+      <c r="I49" s="3">
         <v>56800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>87500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4038,8 +4148,8 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -4065,8 +4175,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4154,8 +4267,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4243,8 +4359,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4252,71 +4371,71 @@
         <v>500</v>
       </c>
       <c r="E52" s="3">
+        <v>500</v>
+      </c>
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4000</v>
       </c>
-      <c r="G52" s="3">
-        <v>800</v>
-      </c>
       <c r="H52" s="3">
-        <v>1400</v>
+        <v>12300</v>
       </c>
       <c r="I52" s="3">
         <v>1400</v>
       </c>
       <c r="J52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K52" s="3">
         <v>1300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1400</v>
       </c>
       <c r="L52" s="3">
         <v>1400</v>
       </c>
       <c r="M52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N52" s="3">
         <v>1300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1300</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1200</v>
       </c>
       <c r="S52" s="3">
         <v>1200</v>
       </c>
       <c r="T52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U52" s="3">
         <v>1800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>600</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4332,8 +4451,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4421,80 +4543,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>190100</v>
+      </c>
+      <c r="E54" s="3">
         <v>190900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>191700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>196000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>159500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>178300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>208800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>189800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>203000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>208500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>210800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>218400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>242600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>249300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>247000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>251200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>260900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>166300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>166500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>171800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>178800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>43400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>39900</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4510,8 +4635,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4543,8 +4671,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4576,80 +4705,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3800</v>
       </c>
-      <c r="G57" s="3">
-        <v>2100</v>
-      </c>
       <c r="H57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I57" s="3">
         <v>1900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,47 +4795,50 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
-        <v>1900</v>
-      </c>
       <c r="H58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I58" s="3">
         <v>2300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2000</v>
       </c>
       <c r="L58" s="3">
         <v>2000</v>
       </c>
       <c r="M58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N58" s="3">
         <v>1900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1700</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4728,17 +4861,17 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4754,80 +4887,83 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E59" s="3">
         <v>32800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10500</v>
       </c>
-      <c r="G59" s="3">
-        <v>13100</v>
-      </c>
       <c r="H59" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I59" s="3">
         <v>14800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5600</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4843,80 +4979,83 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E60" s="3">
         <v>41500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8500</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,8 +5071,11 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4941,37 +5083,37 @@
         <v>3900</v>
       </c>
       <c r="E61" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F61" s="3">
         <v>4000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2700</v>
       </c>
-      <c r="G61" s="3">
-        <v>4700</v>
-      </c>
       <c r="H61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I61" s="3">
         <v>4900</v>
-      </c>
-      <c r="I61" s="3">
-        <v>3400</v>
       </c>
       <c r="J61" s="3">
         <v>3400</v>
       </c>
       <c r="K61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L61" s="3">
         <v>3900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5500</v>
-      </c>
-      <c r="O61" s="3">
-        <v>15000</v>
       </c>
       <c r="P61" s="3">
         <v>15000</v>
@@ -4995,17 +5137,17 @@
         <v>15000</v>
       </c>
       <c r="W61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="X61" s="3">
         <v>14300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>12800</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5021,80 +5163,83 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
         <v>0</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>4800</v>
       </c>
-      <c r="G62" s="3">
-        <v>2300</v>
-      </c>
       <c r="H62" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I62" s="3">
         <v>3400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15500</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>15500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>14200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>14600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>14300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11500</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5110,8 +5255,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5199,8 +5347,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5288,8 +5439,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5377,80 +5531,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E66" s="3">
         <v>54600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>44900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>44400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>46300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>43500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>39800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>38400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>39800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>37900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32800</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,8 +5623,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5499,8 +5659,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5588,8 +5749,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5677,8 +5841,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5743,13 +5910,13 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>71100</v>
       </c>
       <c r="Z70" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="AA70" s="3">
         <v>0</v>
@@ -5766,8 +5933,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5855,80 +6025,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-223300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-227500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-212500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-199200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-242800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-223400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-194100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-181500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-170600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-163200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-156100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-146700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-134200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-124400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-118200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-110100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-97200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-92000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-84600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-78500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-68200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-66500</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5944,8 +6117,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6033,8 +6209,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6122,8 +6301,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6211,80 +6393,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>143700</v>
+      </c>
+      <c r="E76" s="3">
         <v>136300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>148800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>159400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>114600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>131000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>156400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>156900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>165500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>169900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>174500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>180600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>190600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>196500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>201100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>206800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>214600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>122800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>126700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>133300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>139000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-65600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-64000</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6300,8 +6485,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6389,191 +6577,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>43600</v>
       </c>
-      <c r="G81" s="3">
-        <v>-19400</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3">
         <v>-29300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6605,28 +6802,29 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>1300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>400</v>
       </c>
       <c r="J83" s="3">
         <v>400</v>
@@ -6635,7 +6833,7 @@
         <v>400</v>
       </c>
       <c r="L83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
@@ -6644,13 +6842,13 @@
         <v>300</v>
       </c>
       <c r="O83" s="3">
+        <v>300</v>
+      </c>
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
@@ -6662,40 +6860,43 @@
         <v>300</v>
       </c>
       <c r="U83" s="3">
+        <v>300</v>
+      </c>
+      <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>100</v>
-      </c>
-      <c r="W83" s="3">
-        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
       </c>
       <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>400</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>200</v>
       </c>
       <c r="AA83" s="3">
         <v>200</v>
       </c>
       <c r="AB83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC83" s="3">
         <v>500</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6783,8 +6984,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6872,8 +7076,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6961,8 +7168,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7050,8 +7260,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7139,97 +7352,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="E89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15000</v>
       </c>
-      <c r="G89" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
         <v>-5600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7261,97 +7480,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
       </c>
       <c r="U91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V91" s="3">
         <v>-600</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-300</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7439,8 +7662,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7528,97 +7754,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>5200</v>
-      </c>
-      <c r="E94" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-11600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>50300</v>
       </c>
-      <c r="G94" s="3">
-        <v>800</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-45100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-100</v>
       </c>
       <c r="T94" s="3">
         <v>-100</v>
       </c>
       <c r="U94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7650,8 +7882,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7688,8 +7921,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7739,8 +7972,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7828,8 +8064,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7917,8 +8156,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8006,74 +8248,77 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>400</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L100" s="3">
+        <v>100</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="P100" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>200</v>
+      </c>
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-15400</v>
-      </c>
-      <c r="O100" s="3">
-        <v>400</v>
-      </c>
-      <c r="P100" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="T100" s="3">
+        <v>94500</v>
+      </c>
+      <c r="U100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
-        <v>100</v>
-      </c>
-      <c r="S100" s="3">
-        <v>94500</v>
-      </c>
-      <c r="T100" s="3">
-        <v>500</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>137200</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -8081,27 +8326,30 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>5000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>17200</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -8127,17 +8375,17 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -8151,8 +8399,8 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -8184,93 +8432,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1000</v>
+        <v>7700</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-17400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>35100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-57800</v>
+      </c>
+      <c r="K102" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="L102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M102" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="O102" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="P102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="R102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="S102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-57800</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-16400</v>
-      </c>
-      <c r="K102" s="3">
-        <v>2800</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-14800</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-28200</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-27200</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-19300</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>85300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>139500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>8400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5700</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>MASS</t>
   </si>
@@ -656,414 +656,427 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E8" s="3">
         <v>17400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11800</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>14500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6200</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E9" s="3">
         <v>8200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>6700</v>
       </c>
       <c r="F9" s="3">
         <v>6700</v>
       </c>
       <c r="G9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H9" s="3">
         <v>6200</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
         <v>6700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3200</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E10" s="3">
         <v>9200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5500</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>7800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3000</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1096,100 +1109,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E12" s="3">
         <v>3300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3800</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>4200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5400</v>
-      </c>
-      <c r="M12" s="3">
-        <v>5500</v>
       </c>
       <c r="N12" s="3">
         <v>5500</v>
       </c>
       <c r="O12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="P12" s="3">
         <v>5400</v>
-      </c>
-      <c r="P12" s="3">
-        <v>4700</v>
       </c>
       <c r="Q12" s="3">
         <v>4700</v>
       </c>
       <c r="R12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="S12" s="3">
         <v>4300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>4800</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,49 +1297,52 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-5800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>18400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1339,8 +1359,8 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
@@ -1354,15 +1374,15 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-300</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1372,8 +1392,11 @@
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1384,43 +1407,43 @@
         <v>1100</v>
       </c>
       <c r="F15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G15" s="3">
         <v>1000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1400</v>
       </c>
       <c r="I15" s="3">
         <v>1400</v>
       </c>
       <c r="J15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>700</v>
-      </c>
-      <c r="N15" s="3">
-        <v>600</v>
       </c>
       <c r="O15" s="3">
         <v>600</v>
       </c>
       <c r="P15" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="Q15" s="3">
         <v>100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
+      <c r="R15" s="3">
+        <v>100</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
@@ -1437,8 +1460,8 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1464,8 +1487,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1495,192 +1521,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E17" s="3">
         <v>20400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20300</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
         <v>20600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>19500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13800</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8500</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>-6100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1713,82 +1746,83 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
@@ -1796,8 +1830,8 @@
       <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
+      <c r="AD20" s="3">
+        <v>100</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
@@ -1805,100 +1839,106 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
         <v>0</v>
       </c>
       <c r="AB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1926,24 +1966,24 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1960,144 +2000,150 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
-      </c>
-      <c r="X22" s="3">
-        <v>200</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
       </c>
       <c r="Z22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA22" s="3">
         <v>500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>600</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9800</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
         <v>-23600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2110,17 +2156,17 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>-100</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -2137,8 +2183,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -2173,8 +2219,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2265,192 +2314,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9800</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3">
         <v>-23600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>43600</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
         <v>-29300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2541,37 +2599,40 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>53400</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-5600</v>
-      </c>
-      <c r="J29" s="3">
-        <v>-5000</v>
       </c>
       <c r="K29" s="3">
         <v>-5000</v>
       </c>
       <c r="L29" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2633,8 +2694,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2725,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2817,82 +2884,85 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
@@ -2900,8 +2970,8 @@
       <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
+      <c r="AD32" s="3">
+        <v>-100</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
@@ -2909,100 +2979,106 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>43600</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3">
         <v>-29300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3093,197 +3169,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>43600</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3">
         <v>-29300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3316,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3350,83 +3436,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E41" s="3">
         <v>70500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>62800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>61800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>79200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>45000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>104600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>121000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>118200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>133000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>161200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>188400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>193700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>213000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>223100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>224100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>138800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>141300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>149000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>159200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11300</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3442,49 +3529,52 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E42" s="3">
         <v>42500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>49300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>56800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>45200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>25600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>29600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>24600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>29700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>19700</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
@@ -3498,8 +3588,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3534,83 +3624,86 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E43" s="3">
         <v>11300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>15400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3626,83 +3719,86 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E44" s="3">
         <v>13000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>15300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>15500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>12700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>11700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>11200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>9600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4400</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3814,11 @@
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3729,18 +3828,18 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>10200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3759,42 +3858,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>4700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3810,83 +3909,86 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E46" s="3">
         <v>144600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>144900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>147900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>149000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>103100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>108900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>110400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>161900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>173800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>179800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>181100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>187900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>215600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>223900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>238700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>243000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>252900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>157500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>157200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>163000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>171000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>34400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>31500</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3902,8 +4004,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3943,8 +4048,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3994,49 +4099,52 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E48" s="3">
         <v>8600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>7000</v>
       </c>
       <c r="Q48" s="3">
         <v>7000</v>
@@ -4045,32 +4153,32 @@
         <v>7000</v>
       </c>
       <c r="S48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="T48" s="3">
         <v>7100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7800</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,56 +4194,59 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E49" s="3">
         <v>36400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>37100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>37300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>38000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>38700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>56800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>87500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17200</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4151,8 +4262,8 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -4178,8 +4289,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4270,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4362,83 +4479,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E52" s="3">
         <v>500</v>
       </c>
       <c r="F52" s="3">
+        <v>500</v>
+      </c>
+      <c r="G52" s="3">
         <v>600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1400</v>
       </c>
       <c r="J52" s="3">
         <v>1400</v>
       </c>
       <c r="K52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L52" s="3">
         <v>1300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1400</v>
       </c>
       <c r="M52" s="3">
         <v>1400</v>
       </c>
       <c r="N52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O52" s="3">
         <v>1300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1300</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1200</v>
       </c>
       <c r="T52" s="3">
         <v>1200</v>
       </c>
       <c r="U52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V52" s="3">
         <v>1800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>600</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4454,8 +4574,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4546,83 +4669,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>186700</v>
+      </c>
+      <c r="E54" s="3">
         <v>190100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>190900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>191700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>196000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>159500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>178300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>208800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>189800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>203000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>208500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>210800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>218400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>242600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>249300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>247000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>251200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>260900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>166300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>166500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>171800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>178800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>43400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>39900</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4638,8 +4764,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4672,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4706,83 +4836,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>900</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4798,8 +4929,11 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4807,41 +4941,41 @@
         <v>700</v>
       </c>
       <c r="E58" s="3">
+        <v>700</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2000</v>
       </c>
       <c r="M58" s="3">
         <v>2000</v>
       </c>
       <c r="N58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O58" s="3">
         <v>1900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4864,17 +4998,17 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4890,83 +5024,86 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E59" s="3">
         <v>25800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>32800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5600</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4982,83 +5119,86 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E60" s="3">
         <v>34100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>41500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>15400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8500</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5074,49 +5214,52 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="E61" s="3">
         <v>3900</v>
       </c>
       <c r="F61" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G61" s="3">
         <v>4000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4900</v>
-      </c>
-      <c r="J61" s="3">
-        <v>3400</v>
       </c>
       <c r="K61" s="3">
         <v>3400</v>
       </c>
       <c r="L61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="M61" s="3">
         <v>3900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5500</v>
-      </c>
-      <c r="P61" s="3">
-        <v>15000</v>
       </c>
       <c r="Q61" s="3">
         <v>15000</v>
@@ -5140,17 +5283,17 @@
         <v>15000</v>
       </c>
       <c r="X61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>14300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12800</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5166,8 +5309,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5177,72 +5323,72 @@
       <c r="E62" s="3">
         <v>0</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>4800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>14200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>14600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>14300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11500</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5258,8 +5404,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5350,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5442,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5534,83 +5689,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E66" s="3">
         <v>46400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>52800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>44400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>46300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>43500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>39800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>38400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>39800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>37900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>32800</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5626,8 +5784,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5660,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5752,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5844,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5913,13 +6081,13 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>71100</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>71100</v>
       </c>
       <c r="AA70" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="AB70" s="3">
         <v>0</v>
@@ -5936,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6028,83 +6199,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-235300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-223300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-227500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-212500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-199200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-242800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-223400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-194100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-181500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-170600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-163200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-156100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-146700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-134200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-124400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-118200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-110100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-100600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-97200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-92000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-84600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-78500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-68200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-66500</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6120,8 +6294,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6212,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6304,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6396,83 +6579,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E76" s="3">
         <v>143700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>136300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>148800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>159400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>114600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>131000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>156400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>156900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>165500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>169900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>174500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>180600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>190600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>196500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>201100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>206800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>214600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>122800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>126700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>133300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>139000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-65600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-64000</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6488,8 +6674,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6580,197 +6769,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>43600</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3">
         <v>-29300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6803,31 +7001,32 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>400</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
@@ -6836,7 +7035,7 @@
         <v>400</v>
       </c>
       <c r="M83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
@@ -6845,13 +7044,13 @@
         <v>300</v>
       </c>
       <c r="P83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
@@ -6863,40 +7062,43 @@
         <v>300</v>
       </c>
       <c r="V83" s="3">
+        <v>300</v>
+      </c>
+      <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>100</v>
-      </c>
-      <c r="X83" s="3">
-        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
       </c>
       <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>400</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>200</v>
       </c>
       <c r="AB83" s="3">
         <v>200</v>
       </c>
       <c r="AC83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD83" s="3">
         <v>500</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6987,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7079,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7171,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7263,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7355,100 +7569,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1300</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G89" s="3">
         <v>-5800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-5600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7481,100 +7701,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
       <c r="V91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7665,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7757,100 +7984,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>6800</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F94" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-11600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>50300</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-45100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
       </c>
       <c r="V94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7883,8 +8116,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7924,8 +8158,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7975,8 +8209,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8067,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8159,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8251,77 +8494,80 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>94500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>137200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -8329,30 +8575,33 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>5000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>17200</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -8378,17 +8627,17 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -8402,8 +8651,8 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -8435,96 +8684,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>7700</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G102" s="3">
         <v>-17400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>35100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-57800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-28200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>85300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>139500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>8400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5700</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
